--- a/RangeSayacv4Name.xlsx
+++ b/RangeSayacv4Name.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaank\Downloads\IpekyolRangeSayac\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA217BD-856A-4C69-A7B0-10A4006990E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F486C70E-27E0-4846-AF2F-15AE82815CE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{CC9D8179-E951-433C-AC7D-5FB77520B83B}"/>
   </bookViews>
@@ -2525,6 +2525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB84CC3-E4F8-433E-97ED-4BF62ECF93D3}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I567"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2565,7 +2566,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -2594,7 +2595,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -2623,7 +2624,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
@@ -2652,7 +2653,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>1</v>
       </c>
@@ -2681,7 +2682,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>1</v>
       </c>
@@ -2710,7 +2711,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>1</v>
       </c>
@@ -2739,7 +2740,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>1</v>
       </c>
@@ -2768,7 +2769,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>1</v>
       </c>
@@ -2797,7 +2798,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>1</v>
       </c>
@@ -2826,7 +2827,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>1</v>
       </c>
@@ -2855,7 +2856,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>1</v>
       </c>
@@ -2884,7 +2885,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>1</v>
       </c>
@@ -2913,7 +2914,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>1</v>
       </c>
@@ -2942,7 +2943,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>1</v>
       </c>
@@ -2971,7 +2972,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>1</v>
       </c>
@@ -3000,7 +3001,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>1</v>
       </c>
@@ -3029,7 +3030,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>1</v>
       </c>
@@ -3058,7 +3059,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>1</v>
       </c>
@@ -3087,7 +3088,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>1</v>
       </c>
@@ -3116,7 +3117,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>1</v>
       </c>
@@ -3145,7 +3146,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>1</v>
       </c>
@@ -3174,7 +3175,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>1</v>
       </c>
@@ -3203,7 +3204,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>1</v>
       </c>
@@ -3232,7 +3233,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>1</v>
       </c>
@@ -3261,7 +3262,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>1</v>
       </c>
@@ -3290,7 +3291,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>1</v>
       </c>
@@ -3319,7 +3320,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>1</v>
       </c>
@@ -3348,7 +3349,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>1</v>
       </c>
@@ -3377,7 +3378,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>1</v>
       </c>
@@ -3406,7 +3407,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>1</v>
       </c>
@@ -3435,7 +3436,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>1</v>
       </c>
@@ -3464,7 +3465,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>1</v>
       </c>
@@ -3493,7 +3494,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>1</v>
       </c>
@@ -3522,7 +3523,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>1</v>
       </c>
@@ -3551,7 +3552,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>1</v>
       </c>
@@ -3580,7 +3581,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>1</v>
       </c>
@@ -3609,7 +3610,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>1</v>
       </c>
@@ -3638,7 +3639,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>1</v>
       </c>
@@ -3667,7 +3668,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>1</v>
       </c>
@@ -3696,7 +3697,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>1</v>
       </c>
@@ -3725,7 +3726,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>1</v>
       </c>
@@ -3754,7 +3755,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>1</v>
       </c>
@@ -3783,7 +3784,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>1</v>
       </c>
@@ -3812,7 +3813,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>1</v>
       </c>
@@ -3841,7 +3842,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>1</v>
       </c>
@@ -3870,7 +3871,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>1</v>
       </c>
@@ -3899,7 +3900,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>1</v>
       </c>
@@ -3928,7 +3929,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>1</v>
       </c>
@@ -3957,7 +3958,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>1</v>
       </c>
@@ -3986,7 +3987,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>1</v>
       </c>
@@ -4015,7 +4016,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>1</v>
       </c>
@@ -4044,7 +4045,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>1</v>
       </c>
@@ -4073,7 +4074,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>1</v>
       </c>
@@ -4102,7 +4103,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>1</v>
       </c>
@@ -4131,7 +4132,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>1</v>
       </c>
@@ -4160,7 +4161,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>1</v>
       </c>
@@ -4189,7 +4190,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>1</v>
       </c>
@@ -4218,7 +4219,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>1</v>
       </c>
@@ -4247,7 +4248,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>1</v>
       </c>
@@ -4276,7 +4277,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>1</v>
       </c>
@@ -4305,7 +4306,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>1</v>
       </c>
@@ -4334,7 +4335,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>1</v>
       </c>
@@ -4363,7 +4364,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>1</v>
       </c>
@@ -4392,7 +4393,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>1</v>
       </c>
@@ -4421,7 +4422,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>1</v>
       </c>
@@ -4450,7 +4451,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>1</v>
       </c>
@@ -4479,7 +4480,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>1</v>
       </c>
@@ -4508,7 +4509,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>1</v>
       </c>
@@ -4537,7 +4538,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>1</v>
       </c>
@@ -4566,7 +4567,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>1</v>
       </c>
@@ -4595,7 +4596,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>1</v>
       </c>
@@ -4624,7 +4625,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>1</v>
       </c>
@@ -4653,7 +4654,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>1</v>
       </c>
@@ -4682,7 +4683,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>1</v>
       </c>
@@ -4711,7 +4712,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>1</v>
       </c>
@@ -4740,7 +4741,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>1</v>
       </c>
@@ -4769,7 +4770,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>1</v>
       </c>
@@ -4798,7 +4799,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
         <v>1</v>
       </c>
@@ -4827,7 +4828,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>1</v>
       </c>
@@ -4856,7 +4857,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>1</v>
       </c>
@@ -4885,7 +4886,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>1</v>
       </c>
@@ -4914,7 +4915,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
         <v>1</v>
       </c>
@@ -4943,7 +4944,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
         <v>1</v>
       </c>
@@ -4972,7 +4973,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
         <v>1</v>
       </c>
@@ -5001,7 +5002,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
         <v>1</v>
       </c>
@@ -5030,7 +5031,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
         <v>1</v>
       </c>
@@ -5059,7 +5060,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
         <v>1</v>
       </c>
@@ -5088,7 +5089,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
         <v>1</v>
       </c>
@@ -5117,7 +5118,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
         <v>1</v>
       </c>
@@ -5146,7 +5147,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
         <v>1</v>
       </c>
@@ -5175,7 +5176,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>1</v>
       </c>
@@ -5204,7 +5205,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
         <v>1</v>
       </c>
@@ -5233,7 +5234,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
         <v>1</v>
       </c>
@@ -5262,7 +5263,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
         <v>1</v>
       </c>
@@ -5291,7 +5292,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
         <v>1</v>
       </c>
@@ -5320,7 +5321,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
         <v>1</v>
       </c>
@@ -5349,7 +5350,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
         <v>1</v>
       </c>
@@ -5378,7 +5379,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
         <v>1</v>
       </c>
@@ -5407,7 +5408,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
         <v>1</v>
       </c>
@@ -5436,7 +5437,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
         <v>1</v>
       </c>
@@ -5465,7 +5466,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
         <v>1</v>
       </c>
@@ -5494,7 +5495,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
         <v>1</v>
       </c>
@@ -5523,7 +5524,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
         <v>1</v>
       </c>
@@ -5552,7 +5553,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
         <v>1</v>
       </c>
@@ -5581,7 +5582,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
         <v>1</v>
       </c>
@@ -5610,7 +5611,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
         <v>1</v>
       </c>
@@ -5639,7 +5640,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
         <v>1</v>
       </c>
@@ -5668,7 +5669,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
         <v>1</v>
       </c>
@@ -5697,7 +5698,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
         <v>1</v>
       </c>
@@ -5726,7 +5727,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
         <v>1</v>
       </c>
@@ -5755,7 +5756,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
         <v>1</v>
       </c>
@@ -5784,7 +5785,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
         <v>1</v>
       </c>
@@ -5813,7 +5814,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
         <v>1</v>
       </c>
@@ -5842,7 +5843,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
         <v>1</v>
       </c>
@@ -5871,7 +5872,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
         <v>1</v>
       </c>
@@ -5900,7 +5901,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
         <v>1</v>
       </c>
@@ -5929,7 +5930,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
         <v>1</v>
       </c>
@@ -5958,7 +5959,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
         <v>1</v>
       </c>
@@ -5987,7 +5988,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
         <v>1</v>
       </c>
@@ -6016,7 +6017,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
         <v>1</v>
       </c>
@@ -6045,7 +6046,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
         <v>1</v>
       </c>
@@ -6074,7 +6075,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
         <v>1</v>
       </c>
@@ -6103,7 +6104,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
         <v>1</v>
       </c>
@@ -6132,7 +6133,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
         <v>1</v>
       </c>
@@ -6161,7 +6162,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
         <v>1</v>
       </c>
@@ -6190,7 +6191,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
         <v>1</v>
       </c>
@@ -6219,7 +6220,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
         <v>1</v>
       </c>
@@ -6248,7 +6249,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
         <v>1</v>
       </c>
@@ -6277,7 +6278,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
         <v>1</v>
       </c>
@@ -6306,7 +6307,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
         <v>1</v>
       </c>
@@ -6335,7 +6336,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
         <v>1</v>
       </c>
@@ -6364,7 +6365,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
         <v>1</v>
       </c>
@@ -6393,7 +6394,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
         <v>1</v>
       </c>
@@ -6422,7 +6423,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
         <v>1</v>
       </c>
@@ -6451,7 +6452,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
         <v>1</v>
       </c>
@@ -6480,7 +6481,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
         <v>1</v>
       </c>
@@ -6509,7 +6510,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
         <v>1</v>
       </c>
@@ -6538,7 +6539,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
         <v>1</v>
       </c>
@@ -6567,7 +6568,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
         <v>1</v>
       </c>
@@ -6596,7 +6597,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
         <v>1</v>
       </c>
@@ -6625,7 +6626,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
         <v>1</v>
       </c>
@@ -6654,7 +6655,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
         <v>1</v>
       </c>
@@ -6683,7 +6684,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
         <v>1</v>
       </c>
@@ -6712,7 +6713,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
         <v>1</v>
       </c>
@@ -6741,7 +6742,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
         <v>1</v>
       </c>
@@ -6770,7 +6771,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
         <v>1</v>
       </c>
@@ -6799,7 +6800,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
         <v>1</v>
       </c>
@@ -6828,7 +6829,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
         <v>1</v>
       </c>
@@ -6857,7 +6858,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
         <v>1</v>
       </c>
@@ -6886,7 +6887,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
         <v>1</v>
       </c>
@@ -6915,7 +6916,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
         <v>1</v>
       </c>
@@ -6944,7 +6945,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
         <v>1</v>
       </c>
@@ -6973,7 +6974,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
         <v>1</v>
       </c>
@@ -7002,7 +7003,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
         <v>1</v>
       </c>
@@ -7031,7 +7032,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
         <v>1</v>
       </c>
@@ -7060,7 +7061,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
         <v>1</v>
       </c>
@@ -7089,7 +7090,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
         <v>1</v>
       </c>
@@ -7118,7 +7119,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
         <v>1</v>
       </c>
@@ -7147,7 +7148,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
         <v>1</v>
       </c>
@@ -7176,7 +7177,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
         <v>1</v>
       </c>
@@ -7205,7 +7206,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
         <v>1</v>
       </c>
@@ -7234,7 +7235,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
         <v>1</v>
       </c>
@@ -7263,7 +7264,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
         <v>1</v>
       </c>
@@ -7292,7 +7293,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
         <v>1</v>
       </c>
@@ -7321,7 +7322,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
         <v>1</v>
       </c>
@@ -7350,7 +7351,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
         <v>1</v>
       </c>
@@ -7379,7 +7380,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
         <v>1</v>
       </c>
@@ -7408,7 +7409,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
         <v>1</v>
       </c>
@@ -7437,7 +7438,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
         <v>1</v>
       </c>
@@ -7466,7 +7467,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
         <v>1</v>
       </c>
@@ -7495,7 +7496,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
         <v>1</v>
       </c>
@@ -7524,7 +7525,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
         <v>1</v>
       </c>
@@ -7553,7 +7554,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
         <v>1</v>
       </c>
@@ -7582,7 +7583,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
         <v>1</v>
       </c>
@@ -7611,7 +7612,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
         <v>1</v>
       </c>
@@ -7640,7 +7641,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
         <v>1</v>
       </c>
@@ -7669,7 +7670,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
         <v>1</v>
       </c>
@@ -7698,7 +7699,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
         <v>1</v>
       </c>
@@ -7727,7 +7728,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
         <v>1</v>
       </c>
@@ -7756,7 +7757,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
         <v>1</v>
       </c>
@@ -7785,7 +7786,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
         <v>1</v>
       </c>
@@ -7814,7 +7815,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
         <v>1</v>
       </c>
@@ -7843,7 +7844,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
         <v>1</v>
       </c>
@@ -7872,7 +7873,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
         <v>1</v>
       </c>
@@ -7901,7 +7902,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
         <v>1</v>
       </c>
@@ -7930,7 +7931,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
         <v>1</v>
       </c>
@@ -7959,7 +7960,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
         <v>1</v>
       </c>
@@ -7988,7 +7989,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
         <v>1</v>
       </c>
@@ -8017,7 +8018,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
         <v>1</v>
       </c>
@@ -8046,7 +8047,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
         <v>1</v>
       </c>
@@ -8075,7 +8076,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
         <v>1</v>
       </c>
@@ -8104,7 +8105,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
         <v>1</v>
       </c>
@@ -8133,7 +8134,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
         <v>1</v>
       </c>
@@ -8162,7 +8163,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
         <v>1</v>
       </c>
@@ -8191,7 +8192,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
         <v>1</v>
       </c>
@@ -8220,7 +8221,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
         <v>1</v>
       </c>
@@ -8249,7 +8250,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
         <v>1</v>
       </c>
@@ -8278,7 +8279,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
         <v>1</v>
       </c>
@@ -8307,7 +8308,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
         <v>1</v>
       </c>
@@ -8336,7 +8337,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
         <v>1</v>
       </c>
@@ -8365,7 +8366,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
         <v>1</v>
       </c>
@@ -8394,7 +8395,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
         <v>1</v>
       </c>
@@ -8423,7 +8424,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
         <v>1</v>
       </c>
@@ -8452,7 +8453,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
         <v>1</v>
       </c>
@@ -8481,7 +8482,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
         <v>1</v>
       </c>
@@ -8510,7 +8511,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
         <v>1</v>
       </c>
@@ -8539,7 +8540,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
         <v>1</v>
       </c>
@@ -8568,7 +8569,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
         <v>1</v>
       </c>
@@ -8597,7 +8598,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
         <v>1</v>
       </c>
@@ -8626,7 +8627,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
         <v>1</v>
       </c>
@@ -8655,7 +8656,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
         <v>1</v>
       </c>
@@ -8684,7 +8685,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
         <v>1</v>
       </c>
@@ -8713,7 +8714,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
         <v>1</v>
       </c>
@@ -8742,7 +8743,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
         <v>1</v>
       </c>
@@ -8771,7 +8772,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
         <v>1</v>
       </c>
@@ -8800,7 +8801,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
         <v>1</v>
       </c>
@@ -8829,7 +8830,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
         <v>1</v>
       </c>
@@ -8858,7 +8859,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
         <v>1</v>
       </c>
@@ -8887,7 +8888,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
         <v>1</v>
       </c>
@@ -8916,7 +8917,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
         <v>1</v>
       </c>
@@ -8945,7 +8946,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
         <v>1</v>
       </c>
@@ -8974,7 +8975,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
         <v>1</v>
       </c>
@@ -9003,7 +9004,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
         <v>1</v>
       </c>
@@ -9032,7 +9033,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
         <v>1</v>
       </c>
@@ -9061,7 +9062,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
         <v>1</v>
       </c>
@@ -9090,7 +9091,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
         <v>1</v>
       </c>
@@ -9119,7 +9120,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
         <v>1</v>
       </c>
@@ -9148,7 +9149,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
         <v>1</v>
       </c>
@@ -9177,7 +9178,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
         <v>1</v>
       </c>
@@ -9206,7 +9207,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
         <v>1</v>
       </c>
@@ -9235,7 +9236,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
         <v>1</v>
       </c>
@@ -9264,7 +9265,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
         <v>1</v>
       </c>
@@ -9293,7 +9294,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
         <v>1</v>
       </c>
@@ -9322,7 +9323,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
         <v>1</v>
       </c>
@@ -9351,7 +9352,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
         <v>1</v>
       </c>
@@ -9380,7 +9381,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
         <v>1</v>
       </c>
@@ -9409,7 +9410,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
         <v>1</v>
       </c>
@@ -9438,7 +9439,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
         <v>1</v>
       </c>
@@ -9467,7 +9468,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
         <v>1</v>
       </c>
@@ -9496,7 +9497,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
         <v>1</v>
       </c>
@@ -9525,7 +9526,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
         <v>1</v>
       </c>
@@ -9554,7 +9555,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
         <v>1</v>
       </c>
@@ -9583,7 +9584,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
         <v>1</v>
       </c>
@@ -9612,7 +9613,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
         <v>1</v>
       </c>
@@ -9641,7 +9642,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
         <v>1</v>
       </c>
@@ -9670,7 +9671,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
         <v>1</v>
       </c>
@@ -9699,7 +9700,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
         <v>1</v>
       </c>
@@ -9728,7 +9729,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
         <v>1</v>
       </c>
@@ -9757,7 +9758,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
         <v>1</v>
       </c>
@@ -9786,7 +9787,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
         <v>1</v>
       </c>
@@ -9815,7 +9816,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
         <v>1</v>
       </c>
@@ -9844,7 +9845,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="4" t="s">
         <v>1</v>
       </c>
@@ -9873,7 +9874,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
         <v>1</v>
       </c>
@@ -9902,7 +9903,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="4" t="s">
         <v>1</v>
       </c>
@@ -9931,7 +9932,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
         <v>1</v>
       </c>
@@ -9960,7 +9961,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="4" t="s">
         <v>1</v>
       </c>
@@ -9989,7 +9990,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
         <v>1</v>
       </c>
@@ -10018,7 +10019,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="4" t="s">
         <v>1</v>
       </c>
@@ -10047,7 +10048,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
         <v>1</v>
       </c>
@@ -10076,7 +10077,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="4" t="s">
         <v>1</v>
       </c>
@@ -10105,7 +10106,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="4" t="s">
         <v>1</v>
       </c>
@@ -10134,7 +10135,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="4" t="s">
         <v>1</v>
       </c>
@@ -10163,7 +10164,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="4" t="s">
         <v>1</v>
       </c>
@@ -10192,7 +10193,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="4" t="s">
         <v>1</v>
       </c>
@@ -10221,7 +10222,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="4" t="s">
         <v>1</v>
       </c>
@@ -10250,7 +10251,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="4" t="s">
         <v>1</v>
       </c>
@@ -10279,7 +10280,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="4" t="s">
         <v>1</v>
       </c>
@@ -10308,7 +10309,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="4" t="s">
         <v>1</v>
       </c>
@@ -10337,7 +10338,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="4" t="s">
         <v>1</v>
       </c>
@@ -10366,7 +10367,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="4" t="s">
         <v>1</v>
       </c>
@@ -10395,7 +10396,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="4" t="s">
         <v>1</v>
       </c>
@@ -10424,7 +10425,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="4" t="s">
         <v>1</v>
       </c>
@@ -10453,7 +10454,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="4" t="s">
         <v>1</v>
       </c>
@@ -10482,7 +10483,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="4" t="s">
         <v>1</v>
       </c>
@@ -10511,7 +10512,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="4" t="s">
         <v>1</v>
       </c>
@@ -10540,7 +10541,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="4" t="s">
         <v>1</v>
       </c>
@@ -10569,7 +10570,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="4" t="s">
         <v>1</v>
       </c>
@@ -10598,7 +10599,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="4" t="s">
         <v>1</v>
       </c>
@@ -10627,7 +10628,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="4" t="s">
         <v>1</v>
       </c>
@@ -10656,7 +10657,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="4" t="s">
         <v>1</v>
       </c>
@@ -10685,7 +10686,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="4" t="s">
         <v>1</v>
       </c>
@@ -10714,7 +10715,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="4" t="s">
         <v>1</v>
       </c>
@@ -10743,7 +10744,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="4" t="s">
         <v>1</v>
       </c>
@@ -10772,7 +10773,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="4" t="s">
         <v>1</v>
       </c>
@@ -10801,7 +10802,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="4" t="s">
         <v>1</v>
       </c>
@@ -10830,7 +10831,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="4" t="s">
         <v>1</v>
       </c>
@@ -10859,7 +10860,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="4" t="s">
         <v>1</v>
       </c>
@@ -10888,7 +10889,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="4" t="s">
         <v>1</v>
       </c>
@@ -10917,7 +10918,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="4" t="s">
         <v>1</v>
       </c>
@@ -10946,7 +10947,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="4" t="s">
         <v>1</v>
       </c>
@@ -10975,7 +10976,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="4" t="s">
         <v>1</v>
       </c>
@@ -11004,7 +11005,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="4" t="s">
         <v>1</v>
       </c>
@@ -11033,7 +11034,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="4" t="s">
         <v>1</v>
       </c>
@@ -11062,7 +11063,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="4" t="s">
         <v>1</v>
       </c>
@@ -11091,7 +11092,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="4" t="s">
         <v>1</v>
       </c>
@@ -11120,7 +11121,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="4" t="s">
         <v>1</v>
       </c>
@@ -11149,7 +11150,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="4" t="s">
         <v>1</v>
       </c>
@@ -11178,7 +11179,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="4" t="s">
         <v>1</v>
       </c>
@@ -11207,7 +11208,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="4" t="s">
         <v>1</v>
       </c>
@@ -11236,7 +11237,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="4" t="s">
         <v>334</v>
       </c>
@@ -11265,7 +11266,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="4" t="s">
         <v>334</v>
       </c>
@@ -11294,7 +11295,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="4" t="s">
         <v>334</v>
       </c>
@@ -11323,7 +11324,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="4" t="s">
         <v>334</v>
       </c>
@@ -11352,7 +11353,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="4" t="s">
         <v>334</v>
       </c>
@@ -11381,7 +11382,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="4" t="s">
         <v>334</v>
       </c>
@@ -11410,7 +11411,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="4" t="s">
         <v>334</v>
       </c>
@@ -11439,7 +11440,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="4" t="s">
         <v>334</v>
       </c>
@@ -11468,7 +11469,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="4" t="s">
         <v>334</v>
       </c>
@@ -11497,7 +11498,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="4" t="s">
         <v>334</v>
       </c>
@@ -11526,7 +11527,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="4" t="s">
         <v>334</v>
       </c>
@@ -11555,7 +11556,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="4" t="s">
         <v>334</v>
       </c>
@@ -11584,7 +11585,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="4" t="s">
         <v>334</v>
       </c>
@@ -11613,7 +11614,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="4" t="s">
         <v>334</v>
       </c>
@@ -11642,7 +11643,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="4" t="s">
         <v>334</v>
       </c>
@@ -11671,7 +11672,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="4" t="s">
         <v>334</v>
       </c>
@@ -11700,7 +11701,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="4" t="s">
         <v>334</v>
       </c>
@@ -11729,7 +11730,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="4" t="s">
         <v>334</v>
       </c>
@@ -11758,7 +11759,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="4" t="s">
         <v>334</v>
       </c>
@@ -11787,7 +11788,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="4" t="s">
         <v>334</v>
       </c>
@@ -11816,7 +11817,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="4" t="s">
         <v>334</v>
       </c>
@@ -11845,7 +11846,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="4" t="s">
         <v>334</v>
       </c>
@@ -11874,7 +11875,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="4" t="s">
         <v>334</v>
       </c>
@@ -11903,7 +11904,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="4" t="s">
         <v>334</v>
       </c>
@@ -11932,7 +11933,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="4" t="s">
         <v>334</v>
       </c>
@@ -11961,7 +11962,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="4" t="s">
         <v>334</v>
       </c>
@@ -11990,7 +11991,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="4" t="s">
         <v>334</v>
       </c>
@@ -12019,7 +12020,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="4" t="s">
         <v>334</v>
       </c>
@@ -12048,7 +12049,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="4" t="s">
         <v>334</v>
       </c>
@@ -12077,7 +12078,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="4" t="s">
         <v>334</v>
       </c>
@@ -12106,7 +12107,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="4" t="s">
         <v>334</v>
       </c>
@@ -12135,7 +12136,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="4" t="s">
         <v>334</v>
       </c>
@@ -12164,7 +12165,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="4" t="s">
         <v>334</v>
       </c>
@@ -12193,7 +12194,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="4" t="s">
         <v>334</v>
       </c>
@@ -12222,7 +12223,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="4" t="s">
         <v>334</v>
       </c>
@@ -12251,7 +12252,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="4" t="s">
         <v>334</v>
       </c>
@@ -12280,7 +12281,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="4" t="s">
         <v>334</v>
       </c>
@@ -12309,7 +12310,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="4" t="s">
         <v>334</v>
       </c>
@@ -12338,7 +12339,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="4" t="s">
         <v>334</v>
       </c>
@@ -12367,7 +12368,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="4" t="s">
         <v>334</v>
       </c>
@@ -12396,7 +12397,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="4" t="s">
         <v>334</v>
       </c>
@@ -12454,7 +12455,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="4" t="s">
         <v>334</v>
       </c>
@@ -12483,7 +12484,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="4" t="s">
         <v>334</v>
       </c>
@@ -12512,7 +12513,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="4" t="s">
         <v>334</v>
       </c>
@@ -12541,7 +12542,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="4" t="s">
         <v>334</v>
       </c>
@@ -12570,7 +12571,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="4" t="s">
         <v>334</v>
       </c>
@@ -12599,7 +12600,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="4" t="s">
         <v>334</v>
       </c>
@@ -12628,7 +12629,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="4" t="s">
         <v>334</v>
       </c>
@@ -12657,7 +12658,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="4" t="s">
         <v>334</v>
       </c>
@@ -12686,7 +12687,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="4" t="s">
         <v>334</v>
       </c>
@@ -12715,7 +12716,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="4" t="s">
         <v>334</v>
       </c>
@@ -12744,7 +12745,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="4" t="s">
         <v>334</v>
       </c>
@@ -12773,7 +12774,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="4" t="s">
         <v>334</v>
       </c>
@@ -12802,7 +12803,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="4" t="s">
         <v>334</v>
       </c>
@@ -12831,7 +12832,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="4" t="s">
         <v>334</v>
       </c>
@@ -12889,7 +12890,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="4" t="s">
         <v>334</v>
       </c>
@@ -12918,7 +12919,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="4" t="s">
         <v>334</v>
       </c>
@@ -12947,7 +12948,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="4" t="s">
         <v>334</v>
       </c>
@@ -12976,7 +12977,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="4" t="s">
         <v>334</v>
       </c>
@@ -13005,7 +13006,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="4" t="s">
         <v>334</v>
       </c>
@@ -13034,7 +13035,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="4" t="s">
         <v>334</v>
       </c>
@@ -13063,7 +13064,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="4" t="s">
         <v>334</v>
       </c>
@@ -13092,7 +13093,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="4" t="s">
         <v>334</v>
       </c>
@@ -13121,7 +13122,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="4" t="s">
         <v>334</v>
       </c>
@@ -13150,7 +13151,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="4" t="s">
         <v>334</v>
       </c>
@@ -13179,7 +13180,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="4" t="s">
         <v>334</v>
       </c>
@@ -13208,7 +13209,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="4" t="s">
         <v>334</v>
       </c>
@@ -13237,7 +13238,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="4" t="s">
         <v>334</v>
       </c>
@@ -13266,7 +13267,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="4" t="s">
         <v>334</v>
       </c>
@@ -13295,7 +13296,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="4" t="s">
         <v>334</v>
       </c>
@@ -13324,7 +13325,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="4" t="s">
         <v>334</v>
       </c>
@@ -13353,7 +13354,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="4" t="s">
         <v>334</v>
       </c>
@@ -13382,7 +13383,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="4" t="s">
         <v>334</v>
       </c>
@@ -13411,7 +13412,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="4" t="s">
         <v>334</v>
       </c>
@@ -13440,7 +13441,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="4" t="s">
         <v>334</v>
       </c>
@@ -13469,7 +13470,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="4" t="s">
         <v>334</v>
       </c>
@@ -13498,7 +13499,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="4" t="s">
         <v>334</v>
       </c>
@@ -13527,7 +13528,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="4" t="s">
         <v>334</v>
       </c>
@@ -13556,7 +13557,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="4" t="s">
         <v>334</v>
       </c>
@@ -13585,7 +13586,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="4" t="s">
         <v>334</v>
       </c>
@@ -13614,7 +13615,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="4" t="s">
         <v>334</v>
       </c>
@@ -13643,7 +13644,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="4" t="s">
         <v>334</v>
       </c>
@@ -13672,7 +13673,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="4" t="s">
         <v>334</v>
       </c>
@@ -13701,7 +13702,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="4" t="s">
         <v>334</v>
       </c>
@@ -13730,7 +13731,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="4" t="s">
         <v>334</v>
       </c>
@@ -13759,7 +13760,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="4" t="s">
         <v>334</v>
       </c>
@@ -13817,7 +13818,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="4" t="s">
         <v>334</v>
       </c>
@@ -13846,7 +13847,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="4" t="s">
         <v>334</v>
       </c>
@@ -13875,7 +13876,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="4" t="s">
         <v>334</v>
       </c>
@@ -13904,7 +13905,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="4" t="s">
         <v>334</v>
       </c>
@@ -13933,7 +13934,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="4" t="s">
         <v>334</v>
       </c>
@@ -13962,7 +13963,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="4" t="s">
         <v>334</v>
       </c>
@@ -13991,7 +13992,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="4" t="s">
         <v>334</v>
       </c>
@@ -14020,7 +14021,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="4" t="s">
         <v>334</v>
       </c>
@@ -14049,7 +14050,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="4" t="s">
         <v>334</v>
       </c>
@@ -14078,7 +14079,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="4" t="s">
         <v>334</v>
       </c>
@@ -14107,7 +14108,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="4" t="s">
         <v>334</v>
       </c>
@@ -14136,7 +14137,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="4" t="s">
         <v>334</v>
       </c>
@@ -14165,7 +14166,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="4" t="s">
         <v>334</v>
       </c>
@@ -14194,7 +14195,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="4" t="s">
         <v>334</v>
       </c>
@@ -14223,7 +14224,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="4" t="s">
         <v>334</v>
       </c>
@@ -14252,7 +14253,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="4" t="s">
         <v>334</v>
       </c>
@@ -14281,7 +14282,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="4" t="s">
         <v>334</v>
       </c>
@@ -14310,7 +14311,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="4" t="s">
         <v>334</v>
       </c>
@@ -14339,7 +14340,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="4" t="s">
         <v>334</v>
       </c>
@@ -14368,7 +14369,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="4" t="s">
         <v>334</v>
       </c>
@@ -14397,7 +14398,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="4" t="s">
         <v>334</v>
       </c>
@@ -14426,7 +14427,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="4" t="s">
         <v>334</v>
       </c>
@@ -14455,7 +14456,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="4" t="s">
         <v>334</v>
       </c>
@@ -14484,7 +14485,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="4" t="s">
         <v>334</v>
       </c>
@@ -14513,7 +14514,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="4" t="s">
         <v>334</v>
       </c>
@@ -14542,7 +14543,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="4" t="s">
         <v>334</v>
       </c>
@@ -14571,7 +14572,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="4" t="s">
         <v>334</v>
       </c>
@@ -14600,7 +14601,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="4" t="s">
         <v>334</v>
       </c>
@@ -14629,7 +14630,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="4" t="s">
         <v>334</v>
       </c>
@@ -14658,7 +14659,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="4" t="s">
         <v>334</v>
       </c>
@@ -14687,7 +14688,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" s="4" t="s">
         <v>334</v>
       </c>
@@ -14716,7 +14717,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" s="4" t="s">
         <v>334</v>
       </c>
@@ -14745,7 +14746,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" s="4" t="s">
         <v>334</v>
       </c>
@@ -14774,7 +14775,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" s="4" t="s">
         <v>334</v>
       </c>
@@ -14803,7 +14804,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" s="4" t="s">
         <v>334</v>
       </c>
@@ -14832,7 +14833,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" s="4" t="s">
         <v>334</v>
       </c>
@@ -14861,7 +14862,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" s="4" t="s">
         <v>334</v>
       </c>
@@ -14890,7 +14891,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" s="4" t="s">
         <v>334</v>
       </c>
@@ -14919,7 +14920,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" s="4" t="s">
         <v>334</v>
       </c>
@@ -14977,7 +14978,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" s="4" t="s">
         <v>334</v>
       </c>
@@ -15006,7 +15007,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" s="4" t="s">
         <v>334</v>
       </c>
@@ -15035,7 +15036,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" s="4" t="s">
         <v>334</v>
       </c>
@@ -15064,7 +15065,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" s="4" t="s">
         <v>334</v>
       </c>
@@ -15093,7 +15094,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="4" t="s">
         <v>334</v>
       </c>
@@ -15122,7 +15123,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="4" t="s">
         <v>334</v>
       </c>
@@ -15151,7 +15152,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" s="4" t="s">
         <v>334</v>
       </c>
@@ -15180,7 +15181,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" s="4" t="s">
         <v>334</v>
       </c>
@@ -15209,7 +15210,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" s="4" t="s">
         <v>334</v>
       </c>
@@ -15238,7 +15239,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" s="4" t="s">
         <v>334</v>
       </c>
@@ -15267,7 +15268,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" s="4" t="s">
         <v>334</v>
       </c>
@@ -15296,7 +15297,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" s="4" t="s">
         <v>334</v>
       </c>
@@ -15325,7 +15326,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" s="4" t="s">
         <v>334</v>
       </c>
@@ -15354,7 +15355,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" s="4" t="s">
         <v>334</v>
       </c>
@@ -15383,7 +15384,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" s="4" t="s">
         <v>334</v>
       </c>
@@ -15412,7 +15413,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" s="4" t="s">
         <v>334</v>
       </c>
@@ -15441,7 +15442,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" s="4" t="s">
         <v>334</v>
       </c>
@@ -15470,7 +15471,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" s="4" t="s">
         <v>334</v>
       </c>
@@ -15499,7 +15500,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" s="4" t="s">
         <v>334</v>
       </c>
@@ -15528,7 +15529,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" s="4" t="s">
         <v>334</v>
       </c>
@@ -15557,7 +15558,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" s="4" t="s">
         <v>334</v>
       </c>
@@ -15586,7 +15587,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" s="4" t="s">
         <v>334</v>
       </c>
@@ -15615,7 +15616,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" s="4" t="s">
         <v>334</v>
       </c>
@@ -15644,7 +15645,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" s="4" t="s">
         <v>334</v>
       </c>
@@ -15673,7 +15674,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" s="4" t="s">
         <v>334</v>
       </c>
@@ -15702,7 +15703,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" s="4" t="s">
         <v>334</v>
       </c>
@@ -15731,7 +15732,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" s="4" t="s">
         <v>334</v>
       </c>
@@ -15760,7 +15761,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" s="4" t="s">
         <v>334</v>
       </c>
@@ -15789,7 +15790,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" s="4" t="s">
         <v>334</v>
       </c>
@@ -15818,7 +15819,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" s="4" t="s">
         <v>334</v>
       </c>
@@ -15847,7 +15848,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" s="4" t="s">
         <v>334</v>
       </c>
@@ -15876,7 +15877,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" s="4" t="s">
         <v>334</v>
       </c>
@@ -15905,7 +15906,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" s="4" t="s">
         <v>334</v>
       </c>
@@ -15934,7 +15935,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" s="4" t="s">
         <v>334</v>
       </c>
@@ -15963,7 +15964,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" s="4" t="s">
         <v>334</v>
       </c>
@@ -15992,7 +15993,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" s="4" t="s">
         <v>334</v>
       </c>
@@ -16021,7 +16022,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" s="4" t="s">
         <v>334</v>
       </c>
@@ -16050,7 +16051,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" s="4" t="s">
         <v>334</v>
       </c>
@@ -16079,7 +16080,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" s="4" t="s">
         <v>334</v>
       </c>
@@ -16108,7 +16109,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" s="4" t="s">
         <v>334</v>
       </c>
@@ -16166,7 +16167,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" s="4" t="s">
         <v>334</v>
       </c>
@@ -16195,7 +16196,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" s="4" t="s">
         <v>334</v>
       </c>
@@ -16224,7 +16225,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" s="4" t="s">
         <v>334</v>
       </c>
@@ -16253,7 +16254,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" s="4" t="s">
         <v>334</v>
       </c>
@@ -16282,7 +16283,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" s="4" t="s">
         <v>334</v>
       </c>
@@ -16311,7 +16312,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" s="4" t="s">
         <v>334</v>
       </c>
@@ -16340,7 +16341,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" s="4" t="s">
         <v>334</v>
       </c>
@@ -16369,7 +16370,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" s="4" t="s">
         <v>334</v>
       </c>
@@ -16398,7 +16399,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" s="4" t="s">
         <v>334</v>
       </c>
@@ -16427,7 +16428,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" s="4" t="s">
         <v>334</v>
       </c>
@@ -16456,7 +16457,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" s="4" t="s">
         <v>334</v>
       </c>
@@ -16485,7 +16486,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" s="4" t="s">
         <v>334</v>
       </c>
@@ -16514,7 +16515,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" s="4" t="s">
         <v>334</v>
       </c>
@@ -16543,7 +16544,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" s="4" t="s">
         <v>334</v>
       </c>
@@ -16572,7 +16573,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" s="4" t="s">
         <v>334</v>
       </c>
@@ -16601,7 +16602,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" s="4" t="s">
         <v>334</v>
       </c>
@@ -16630,7 +16631,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" s="4" t="s">
         <v>334</v>
       </c>
@@ -16659,7 +16660,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" s="4" t="s">
         <v>334</v>
       </c>
@@ -16688,7 +16689,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" s="4" t="s">
         <v>334</v>
       </c>
@@ -16717,7 +16718,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" s="4" t="s">
         <v>334</v>
       </c>
@@ -16746,7 +16747,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" s="4" t="s">
         <v>334</v>
       </c>
@@ -16775,7 +16776,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" s="4" t="s">
         <v>334</v>
       </c>
@@ -16804,7 +16805,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" s="4" t="s">
         <v>334</v>
       </c>
@@ -16833,7 +16834,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" s="4" t="s">
         <v>334</v>
       </c>
@@ -16862,7 +16863,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" s="4" t="s">
         <v>334</v>
       </c>
@@ -16891,7 +16892,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" s="4" t="s">
         <v>334</v>
       </c>
@@ -16920,7 +16921,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" s="4" t="s">
         <v>334</v>
       </c>
@@ -16949,7 +16950,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" s="4" t="s">
         <v>334</v>
       </c>
@@ -16978,7 +16979,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" s="4" t="s">
         <v>334</v>
       </c>
@@ -17007,7 +17008,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" s="4" t="s">
         <v>334</v>
       </c>
@@ -17036,7 +17037,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" s="4" t="s">
         <v>334</v>
       </c>
@@ -17065,7 +17066,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" s="4" t="s">
         <v>334</v>
       </c>
@@ -17094,7 +17095,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" s="4" t="s">
         <v>334</v>
       </c>
@@ -17123,7 +17124,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" s="4" t="s">
         <v>334</v>
       </c>
@@ -17152,7 +17153,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" s="4" t="s">
         <v>334</v>
       </c>
@@ -17210,7 +17211,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" s="4" t="s">
         <v>334</v>
       </c>
@@ -17239,7 +17240,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" s="4" t="s">
         <v>334</v>
       </c>
@@ -17268,7 +17269,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" s="4" t="s">
         <v>334</v>
       </c>
@@ -17297,7 +17298,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" s="4" t="s">
         <v>334</v>
       </c>
@@ -17326,7 +17327,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" s="4" t="s">
         <v>334</v>
       </c>
@@ -17355,7 +17356,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" s="4" t="s">
         <v>334</v>
       </c>
@@ -17384,7 +17385,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" s="4" t="s">
         <v>334</v>
       </c>
@@ -17413,7 +17414,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" s="4" t="s">
         <v>334</v>
       </c>
@@ -17442,7 +17443,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" s="4" t="s">
         <v>334</v>
       </c>
@@ -17471,7 +17472,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" s="4" t="s">
         <v>334</v>
       </c>
@@ -17500,7 +17501,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" s="4" t="s">
         <v>334</v>
       </c>
@@ -17529,7 +17530,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" s="4" t="s">
         <v>334</v>
       </c>
@@ -17558,7 +17559,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" s="4" t="s">
         <v>334</v>
       </c>
@@ -17587,7 +17588,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" s="4" t="s">
         <v>334</v>
       </c>
@@ -17616,7 +17617,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" s="4" t="s">
         <v>334</v>
       </c>
@@ -17645,7 +17646,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" s="4" t="s">
         <v>334</v>
       </c>
@@ -17674,7 +17675,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" s="4" t="s">
         <v>334</v>
       </c>
@@ -17703,7 +17704,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" s="4" t="s">
         <v>334</v>
       </c>
@@ -17732,7 +17733,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" s="4" t="s">
         <v>334</v>
       </c>
@@ -17761,7 +17762,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" s="4" t="s">
         <v>334</v>
       </c>
@@ -17790,7 +17791,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" s="4" t="s">
         <v>334</v>
       </c>
@@ -17819,7 +17820,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" s="4" t="s">
         <v>334</v>
       </c>
@@ -17848,7 +17849,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529" s="4" t="s">
         <v>334</v>
       </c>
@@ -17906,7 +17907,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" s="4" t="s">
         <v>334</v>
       </c>
@@ -17935,7 +17936,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" s="4" t="s">
         <v>334</v>
       </c>
@@ -17964,7 +17965,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" s="4" t="s">
         <v>334</v>
       </c>
@@ -17993,7 +17994,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" s="4" t="s">
         <v>334</v>
       </c>
@@ -18022,7 +18023,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" s="4" t="s">
         <v>334</v>
       </c>
@@ -18051,7 +18052,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" s="4" t="s">
         <v>334</v>
       </c>
@@ -18080,7 +18081,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" s="4" t="s">
         <v>334</v>
       </c>
@@ -18109,7 +18110,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" s="4" t="s">
         <v>334</v>
       </c>
@@ -18138,7 +18139,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" s="4" t="s">
         <v>334</v>
       </c>
@@ -18167,7 +18168,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" s="4" t="s">
         <v>334</v>
       </c>
@@ -18196,7 +18197,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" s="4" t="s">
         <v>334</v>
       </c>
@@ -18225,7 +18226,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" s="4" t="s">
         <v>334</v>
       </c>
@@ -18254,7 +18255,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" s="4" t="s">
         <v>334</v>
       </c>
@@ -18283,7 +18284,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" s="4" t="s">
         <v>334</v>
       </c>
@@ -18312,7 +18313,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" s="4" t="s">
         <v>334</v>
       </c>
@@ -18341,7 +18342,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" s="4" t="s">
         <v>334</v>
       </c>
@@ -18370,7 +18371,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" s="4" t="s">
         <v>334</v>
       </c>
@@ -18399,7 +18400,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" s="4" t="s">
         <v>334</v>
       </c>
@@ -18428,7 +18429,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" s="4" t="s">
         <v>334</v>
       </c>
@@ -18457,7 +18458,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" s="4" t="s">
         <v>334</v>
       </c>
@@ -18486,7 +18487,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" s="4" t="s">
         <v>334</v>
       </c>
@@ -18515,7 +18516,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" s="4" t="s">
         <v>334</v>
       </c>
@@ -18544,7 +18545,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" s="4" t="s">
         <v>334</v>
       </c>
@@ -18573,7 +18574,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" s="4" t="s">
         <v>334</v>
       </c>
@@ -18602,7 +18603,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" s="4" t="s">
         <v>334</v>
       </c>
@@ -18631,7 +18632,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" s="4" t="s">
         <v>334</v>
       </c>
@@ -18660,7 +18661,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="557" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" s="4" t="s">
         <v>334</v>
       </c>
@@ -18689,7 +18690,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" s="4" t="s">
         <v>334</v>
       </c>
@@ -18718,7 +18719,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" s="4" t="s">
         <v>334</v>
       </c>
@@ -18747,7 +18748,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" s="4" t="s">
         <v>334</v>
       </c>
@@ -18776,7 +18777,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" s="4" t="s">
         <v>334</v>
       </c>
@@ -18805,7 +18806,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" s="4" t="s">
         <v>334</v>
       </c>
@@ -18834,7 +18835,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" s="4" t="s">
         <v>334</v>
       </c>
@@ -18863,7 +18864,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" s="4" t="s">
         <v>334</v>
       </c>
@@ -18892,7 +18893,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" s="4" t="s">
         <v>334</v>
       </c>
@@ -18921,7 +18922,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" s="4" t="s">
         <v>334</v>
       </c>
@@ -18950,7 +18951,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" s="4" t="s">
         <v>334</v>
       </c>
@@ -18980,7 +18981,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I567" xr:uid="{1CB84CC3-E4F8-433E-97ED-4BF62ECF93D3}"/>
+  <autoFilter ref="A1:I567" xr:uid="{1CB84CC3-E4F8-433E-97ED-4BF62ECF93D3}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="Iconic / Hero"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
